--- a/schemas/PMU_Priorizados_Cliente.xlsx
+++ b/schemas/PMU_Priorizados_Cliente.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\P271\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dairo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45004999-E7E6-40AF-9535-B1267A09BB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B14722-4A57-4E2D-8EB4-1028536FEFC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{60660C94-6AC1-49A0-A23D-9C6558A012E6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{60660C94-6AC1-49A0-A23D-9C6558A012E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Plantilla_Maestro_Usuarios_P" sheetId="1" r:id="rId1"/>
@@ -51,25 +51,25 @@
     <t>TO503</t>
   </si>
   <si>
-    <t>MÃ³vil 1</t>
-  </si>
-  <si>
     <t>CORTE</t>
-  </si>
-  <si>
-    <t>SUSPENSIÃ“N</t>
   </si>
   <si>
     <t>TO501</t>
   </si>
   <si>
-    <t>RECONEXIÃ“N</t>
+    <t>RETIRO DE ACOMETIDA</t>
   </si>
   <si>
-    <t>REVISIÃ“N TÃ‰CNICA</t>
+    <t>Móvil 1</t>
   </si>
   <si>
-    <t>RETIRO DE ACOMETIDA</t>
+    <t>SUSPENSIÓN</t>
+  </si>
+  <si>
+    <t>RECONEXIÓN</t>
+  </si>
+  <si>
+    <t>REVISIÓN TÉCNICA</t>
   </si>
 </sst>
 </file>
@@ -164,9 +164,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -204,7 +204,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -310,7 +310,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -452,7 +452,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -460,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C614042-AA20-42AA-BDD3-A76AECA5D166}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -509,10 +509,10 @@
         <v>7</v>
       </c>
       <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
         <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
       </c>
       <c r="G2" s="4">
         <v>46084</v>
@@ -532,10 +532,10 @@
         <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3" s="4">
         <v>46082</v>
@@ -555,10 +555,10 @@
         <v>7</v>
       </c>
       <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
         <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
       </c>
       <c r="G4" s="4">
         <v>46084</v>
@@ -575,13 +575,13 @@
         <v>150842056</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G5" s="4">
         <v>46085</v>
@@ -598,13 +598,13 @@
         <v>151537324</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" s="4">
         <v>46087</v>
@@ -624,10 +624,10 @@
         <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7" s="4">
         <v>46083</v>
@@ -644,13 +644,13 @@
         <v>151080640</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
         <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
       </c>
       <c r="G8" s="4">
         <v>46087</v>
@@ -670,10 +670,10 @@
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9" s="4">
         <v>46083</v>
@@ -690,13 +690,13 @@
         <v>151539105</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G10" s="4">
         <v>46084</v>
@@ -713,13 +713,13 @@
         <v>150705959</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G11" s="4">
         <v>46083</v>
@@ -736,13 +736,13 @@
         <v>151637799</v>
       </c>
       <c r="D12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
         <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>9</v>
       </c>
       <c r="G12" s="4">
         <v>46083</v>
@@ -759,13 +759,13 @@
         <v>151532139</v>
       </c>
       <c r="D13" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G13" s="4">
         <v>46087</v>
@@ -782,13 +782,13 @@
         <v>150606976</v>
       </c>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G14" s="4">
         <v>46085</v>
@@ -805,13 +805,13 @@
         <v>150720583</v>
       </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" t="s">
         <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>9</v>
       </c>
       <c r="G15" s="4">
         <v>46083</v>
@@ -828,13 +828,13 @@
         <v>151527557</v>
       </c>
       <c r="D16" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
         <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>9</v>
       </c>
       <c r="G16" s="4">
         <v>46084</v>
@@ -851,13 +851,13 @@
         <v>151538895</v>
       </c>
       <c r="D17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" t="s">
         <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>9</v>
       </c>
       <c r="G17" s="4">
         <v>46082</v>
@@ -874,13 +874,13 @@
         <v>151633332</v>
       </c>
       <c r="D18" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="4">
         <v>46085</v>
@@ -900,10 +900,10 @@
         <v>7</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G19" s="4">
         <v>46085</v>
@@ -920,13 +920,13 @@
         <v>151536083</v>
       </c>
       <c r="D20" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G20" s="4">
         <v>46085</v>
@@ -943,13 +943,13 @@
         <v>151637792</v>
       </c>
       <c r="D21" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G21" s="4">
         <v>46084</v>
@@ -966,13 +966,13 @@
         <v>151536059</v>
       </c>
       <c r="D22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G22" s="4">
         <v>46083</v>
@@ -989,13 +989,13 @@
         <v>137331604</v>
       </c>
       <c r="D23" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" t="s">
         <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>9</v>
       </c>
       <c r="G23" s="4">
         <v>46087</v>
@@ -1015,10 +1015,10 @@
         <v>7</v>
       </c>
       <c r="E24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" t="s">
         <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>9</v>
       </c>
       <c r="G24" s="4">
         <v>46087</v>
@@ -1035,13 +1035,13 @@
         <v>151637705</v>
       </c>
       <c r="D25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F25" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G25" s="4">
         <v>46083</v>
@@ -1061,10 +1061,10 @@
         <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F26" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G26" s="4">
         <v>46083</v>
@@ -1084,10 +1084,10 @@
         <v>7</v>
       </c>
       <c r="E27" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G27" s="4">
         <v>46085</v>
@@ -1107,10 +1107,10 @@
         <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F28" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G28" s="4">
         <v>46085</v>
@@ -1127,13 +1127,13 @@
         <v>150712660</v>
       </c>
       <c r="D29" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F29" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G29" s="4">
         <v>46083</v>
@@ -1153,10 +1153,10 @@
         <v>7</v>
       </c>
       <c r="E30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" t="s">
         <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>9</v>
       </c>
       <c r="G30" s="4">
         <v>46085</v>
@@ -1173,13 +1173,13 @@
         <v>150703787</v>
       </c>
       <c r="D31" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F31" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G31" s="4">
         <v>46087</v>
@@ -1196,13 +1196,13 @@
         <v>149328856</v>
       </c>
       <c r="D32" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E32" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F32" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G32" s="4">
         <v>46084</v>
@@ -1222,10 +1222,10 @@
         <v>7</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F33" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G33" s="4">
         <v>46086</v>
@@ -1242,13 +1242,13 @@
         <v>151536458</v>
       </c>
       <c r="D34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F34" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G34" s="4">
         <v>46083</v>
@@ -1265,13 +1265,13 @@
         <v>151537312</v>
       </c>
       <c r="D35" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F35" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G35" s="4">
         <v>46086</v>
@@ -1288,13 +1288,13 @@
         <v>151303845</v>
       </c>
       <c r="D36" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F36" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G36" s="4">
         <v>46082</v>
@@ -1311,13 +1311,13 @@
         <v>151452370</v>
       </c>
       <c r="D37" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E37" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F37" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G37" s="4">
         <v>46082</v>
@@ -1334,13 +1334,13 @@
         <v>151538888</v>
       </c>
       <c r="D38" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E38" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F38" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G38" s="4">
         <v>46082</v>
@@ -1357,13 +1357,13 @@
         <v>150706908</v>
       </c>
       <c r="D39" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E39" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" t="s">
         <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>9</v>
       </c>
       <c r="G39" s="4">
         <v>46085</v>
@@ -1380,13 +1380,13 @@
         <v>145037157</v>
       </c>
       <c r="D40" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E40" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F40" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G40" s="4">
         <v>46085</v>
@@ -1406,10 +1406,10 @@
         <v>7</v>
       </c>
       <c r="E41" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F41" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G41" s="4">
         <v>46085</v>
@@ -1426,13 +1426,13 @@
         <v>151538898</v>
       </c>
       <c r="D42" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F42" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G42" s="4">
         <v>46083</v>
@@ -1449,13 +1449,13 @@
         <v>151635094</v>
       </c>
       <c r="D43" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E43" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F43" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G43" s="4">
         <v>46082</v>
@@ -1472,13 +1472,13 @@
         <v>150723042</v>
       </c>
       <c r="D44" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E44" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F44" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G44" s="4">
         <v>46083</v>
@@ -1495,13 +1495,13 @@
         <v>146930818</v>
       </c>
       <c r="D45" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E45" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F45" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G45" s="4">
         <v>46087</v>
@@ -1521,10 +1521,10 @@
         <v>7</v>
       </c>
       <c r="E46" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" t="s">
         <v>8</v>
-      </c>
-      <c r="F46" t="s">
-        <v>9</v>
       </c>
       <c r="G46" s="4">
         <v>46084</v>
@@ -1541,13 +1541,13 @@
         <v>149924568</v>
       </c>
       <c r="D47" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E47" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F47" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G47" s="4">
         <v>46086</v>
@@ -1564,13 +1564,13 @@
         <v>151528800</v>
       </c>
       <c r="D48" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E48" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F48" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G48" s="4">
         <v>46085</v>
@@ -1587,13 +1587,13 @@
         <v>151637784</v>
       </c>
       <c r="D49" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E49" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" t="s">
         <v>8</v>
-      </c>
-      <c r="F49" t="s">
-        <v>9</v>
       </c>
       <c r="G49" s="4">
         <v>46087</v>
@@ -1610,13 +1610,13 @@
         <v>151530652</v>
       </c>
       <c r="D50" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E50" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F50" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G50" s="4">
         <v>46085</v>
@@ -1636,14 +1636,23 @@
         <v>7</v>
       </c>
       <c r="E51" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F51" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G51" s="4">
         <v>46082</v>
       </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52"/>
+      <c r="B52"/>
+      <c r="C52"/>
+      <c r="D52"/>
+      <c r="E52"/>
+      <c r="F52"/>
+      <c r="G52"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
